--- a/files/RECOMB2026_accepted_posters.xlsx
+++ b/files/RECOMB2026_accepted_posters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zky66\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98912C13-CE65-4B26-BD2A-72D12A4DFBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2615ECC-B759-46CF-AD2F-4A253DCB05FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="208" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="536">
   <si>
     <t>#</t>
   </si>
@@ -1750,16 +1750,117 @@
   </si>
   <si>
     <t>Author could not attend</t>
+  </si>
+  <si>
+    <t>Spatiotemporal cell type deconvolution leveraging tissue structure</t>
+  </si>
+  <si>
+    <t>Macrina Lobo, Ziqi Zhang, Xiuwei Zhang</t>
+  </si>
+  <si>
+    <t>RECOMB-RSG</t>
+  </si>
+  <si>
+    <t>RECOMB-Seq</t>
+  </si>
+  <si>
+    <t>Challenges and pitfalls in the evaluation of Structural Variants callers</t>
+  </si>
+  <si>
+    <t>Tracking Respiratory Syncytial Virus Dynamics in Wastewater During the 2024-2025 Season in Switzerland</t>
+  </si>
+  <si>
+    <t>Improved plasmid classification in assembly graphs</t>
+  </si>
+  <si>
+    <t>CenterStage : A k-mer + Alignment Framework for Systematic Centromere-Proximal Sequence Comparison ​</t>
+  </si>
+  <si>
+    <t>PhaseDancer Web: Scalable Remote Assembly of Complex Genomic Regions</t>
+  </si>
+  <si>
+    <t>Generating Minimum-Density Minimizers</t>
+  </si>
+  <si>
+    <t>Cross-Tissue Probe Threshold Transfer for Mechanistic Gene Regulatory Network Evaluation in Single-Cell Foundation Models</t>
+  </si>
+  <si>
+    <t>Ihor Kendiukhov</t>
+  </si>
+  <si>
+    <t>Luca Denti, Thomas Krannich, Tomas Vinar, Rayan Chikhi, Paola Bonizzoni, Brona Brejova and Fereydoun Hormozdiari</t>
+  </si>
+  <si>
+    <t>Learning Stable Predictors from Weak Supervision under Distribution Shift</t>
+  </si>
+  <si>
+    <t>Mehrdad Shoeibi, Elias Hossain, Ivan Garibay, Niloofar Yousefi</t>
+  </si>
+  <si>
+    <t>SwitchTFI: identifying transcription factors driving cell differentiation</t>
+  </si>
+  <si>
+    <t>Paul Martini, Anne Hartebrodt, Gustavo P. de Almeida, Carl-Philipp Hackstein, Dietmar Zehn, David B. Blumenthal</t>
+  </si>
+  <si>
+    <t>BioGen: An Evidence-Grounded Framework for Interpreting RNA-seq Gene Clusters in Antimicrobial Resistance Research</t>
+  </si>
+  <si>
+    <t>Elias Hossain, Mehrdad Shoeibi, Ivan Garibay, Niloofar Yousefi</t>
+  </si>
+  <si>
+    <t>Secretome: benchmarking cellular localization predictors in prokaryotes</t>
+  </si>
+  <si>
+    <t>Alicja Wojciechowska</t>
+  </si>
+  <si>
+    <t>Sanjeda Sara Jennifer, Elias Hossain, Niloofar Yousefi</t>
+  </si>
+  <si>
+    <t>SeqConnect: A Deep Learning Framework for miRNA-mRNA Interaction Prediction</t>
+  </si>
+  <si>
+    <t>Beyond Edge Ranking: Exact Regulator Set Recovery for Combinatorial Gene Regulation</t>
+  </si>
+  <si>
+    <t>Maryam Rahimimovassagh, Siddhi Kanta Mishra, Ivan Garibay, Niloofar Yousefi</t>
+  </si>
+  <si>
+    <t>Survival-Aware Probabilistic Modeling for Failure-Prone Perturbation Experiments in Regulatory Genomics</t>
+  </si>
+  <si>
+    <t>Arseny Shur, Ido Tziony and Yaron Orenstein</t>
+  </si>
+  <si>
+    <t>Judit Juhász, Bendegúz Filyó, Dániel Krizsán, János Juhász, Giovanni Lorenzin and Balázs Ligeti</t>
+  </si>
+  <si>
+    <t>Barbara Poszewiecka, Antoni Goldstein and Anna Gambin</t>
+  </si>
+  <si>
+    <t>Christina Mulch, Maria Shishimorova, Nuria Marti Gutierrez, Daniel Frana, Crystal Van Dyken, Ying Li, Sang-Goo Lee, Daniel Eyberg, Michelle Nipper, Eryk Andreas, Sergey Tevkin and Shoukhrat Mitalipov ​</t>
+  </si>
+  <si>
+    <t>Auguste Rimaite, Jolinda de Korne-Elenbaas, Adrian Lison, Tanja Stadler, Timothy R. Julian and Niko Beerenwinkel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1796,8 +1897,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1822,8 +1929,14 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1857,15 +1970,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="48"/>
+      </left>
+      <right style="thin">
+        <color indexed="48"/>
+      </right>
+      <top style="thin">
+        <color indexed="48"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="48"/>
+      </left>
+      <right style="thin">
+        <color indexed="48"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="48"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1874,20 +2029,49 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="40% - 着色 1" xfId="3" builtinId="31"/>
     <cellStyle name="60% - 着色 5" xfId="2" builtinId="48"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -2290,7 +2474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E168"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -3419,7 +3603,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>239</v>
       </c>
@@ -3433,7 +3617,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>242</v>
       </c>
@@ -3447,7 +3631,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>245</v>
       </c>
@@ -3461,7 +3645,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>248</v>
       </c>
@@ -3475,7 +3659,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>251</v>
       </c>
@@ -3489,7 +3673,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>254</v>
       </c>
@@ -3503,7 +3687,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>257</v>
       </c>
@@ -3517,7 +3701,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>260</v>
       </c>
@@ -3531,620 +3715,641 @@
         <v>502</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
+    <row r="89" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="s">
+      <c r="D89" s="9" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" s="15" customFormat="1" ht="53.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="10">
+        <v>78</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="53.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="10">
+        <v>763</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="10">
+        <v>791</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" s="15" customFormat="1" ht="53.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="10">
+        <v>818</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>531</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" s="15" customFormat="1" ht="53.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="10">
+        <v>821</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="17">
+        <v>822</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="C95" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="10">
+        <v>824</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B97" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C97" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="2" t="s">
+      <c r="D97" s="13" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B98" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C98" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
+      <c r="D98" s="14" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B99" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C99" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="D92" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
+      <c r="D99" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B100" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C93" s="2" t="s">
+      <c r="C100" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D93" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
+      <c r="D100" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B101" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C101" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
+      <c r="D101" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B102" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C102" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D95" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="3" t="s">
+      <c r="D102" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B103" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C103" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
+      <c r="D103" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B104" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C104" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D97" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="3" t="s">
+      <c r="D104" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B105" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C105" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="D98" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="62.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="2" t="s">
+      <c r="D105" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="62.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B106" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C106" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D99" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
+      <c r="D106" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B107" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C107" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
+      <c r="D107" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B108" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C108" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="s">
+      <c r="D108" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B109" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C109" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="2" t="s">
+      <c r="D109" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="B110" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C110" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="D103" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="3" t="s">
+      <c r="D110" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B111" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="C111" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="D104" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
+      <c r="D111" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B112" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C112" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D105" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="3" t="s">
+      <c r="D112" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B113" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C113" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="D106" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
+      <c r="D113" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B114" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C114" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D107" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="s">
+      <c r="D114" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B115" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C115" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="D108" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="2" t="s">
+      <c r="D115" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B116" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C116" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="D109" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="3" t="s">
+      <c r="D116" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B117" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C117" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="D110" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="2" t="s">
+      <c r="D117" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B118" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C118" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="D111" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="3" t="s">
+      <c r="D118" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B119" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="C119" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="D112" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
+      <c r="D119" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B120" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C120" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D113" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="3" t="s">
+      <c r="D120" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B121" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="C121" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="D114" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="2" t="s">
+      <c r="D121" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B122" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C122" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D115" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="3" t="s">
+      <c r="D122" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B123" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="C123" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="D116" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
+      <c r="D123" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B124" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C124" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="D117" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="3" t="s">
+      <c r="D124" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B125" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="C125" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="D118" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="2" t="s">
+      <c r="D125" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B126" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C119" s="2" t="s">
+      <c r="C126" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D119" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="s">
+      <c r="D126" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B127" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="C127" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="D120" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="2" t="s">
+      <c r="D127" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B128" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C128" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D121" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="3" t="s">
+      <c r="D128" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B129" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="C129" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D122" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" ht="25" x14ac:dyDescent="0.25">
-      <c r="A123" s="6" t="s">
+      <c r="D129" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A130" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="B123" s="6" t="s">
+      <c r="B130" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="C123" s="6" t="s">
+      <c r="C130" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="D123" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="E123" s="7" t="s">
+      <c r="D130" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="E130" s="7" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="25" x14ac:dyDescent="0.25">
-      <c r="A124" s="4" t="s">
+    <row r="131" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B131" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="C131" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="D124" s="5" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="4" t="s">
+      <c r="D131" s="5" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B132" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C132" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="25" x14ac:dyDescent="0.25">
-      <c r="A126" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="25" x14ac:dyDescent="0.25">
-      <c r="A127" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" ht="25" x14ac:dyDescent="0.25">
-      <c r="A128" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" ht="50" x14ac:dyDescent="0.25">
-      <c r="A130" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" ht="25" x14ac:dyDescent="0.25">
-      <c r="A132" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>393</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>503</v>
@@ -4152,13 +4357,13 @@
     </row>
     <row r="133" spans="1:5" ht="25" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>395</v>
+        <v>374</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>396</v>
+        <v>375</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>503</v>
@@ -4166,55 +4371,55 @@
     </row>
     <row r="134" spans="1:5" ht="25" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>397</v>
+        <v>376</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" ht="25" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" ht="50" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>406</v>
+        <v>385</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>407</v>
+        <v>386</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>408</v>
+        <v>387</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>503</v>
@@ -4222,13 +4427,13 @@
     </row>
     <row r="138" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>410</v>
+        <v>389</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>411</v>
+        <v>390</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>503</v>
@@ -4236,13 +4441,13 @@
     </row>
     <row r="139" spans="1:5" ht="25" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>413</v>
+        <v>392</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>503</v>
@@ -4250,41 +4455,41 @@
     </row>
     <row r="140" spans="1:5" ht="25" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>416</v>
+        <v>395</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="D140" s="3" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" ht="25" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>422</v>
+        <v>401</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>503</v>
@@ -4292,373 +4497,618 @@
     </row>
     <row r="143" spans="1:5" ht="25" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="50" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="B143" s="4" t="s">
+      <c r="B150" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="C143" s="4" t="s">
+      <c r="C150" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="D143" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" ht="25" x14ac:dyDescent="0.25">
-      <c r="A144" s="6">
+      <c r="D150" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A151" s="6">
         <v>782</v>
       </c>
-      <c r="B144" s="6" t="s">
+      <c r="B151" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="C144" s="6" t="s">
+      <c r="C151" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="D144" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="E144" s="7" t="s">
+      <c r="D151" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="E151" s="7" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="25" x14ac:dyDescent="0.25">
-      <c r="A145" s="4" t="s">
+    <row r="152" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="B145" s="4" t="s">
+      <c r="B152" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="C145" s="4" t="s">
+      <c r="C152" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="D145" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="4" t="s">
+      <c r="D152" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="B153" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="C146" s="4" t="s">
+      <c r="C153" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="D146" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A147" s="4" t="s">
+      <c r="D153" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="B154" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="C154" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="D147" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" ht="25" x14ac:dyDescent="0.25">
-      <c r="A148" s="4" t="s">
+      <c r="D154" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="B148" s="4" t="s">
+      <c r="B155" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="C148" s="4" t="s">
+      <c r="C155" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="D148" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" ht="25" x14ac:dyDescent="0.25">
-      <c r="A149" s="4" t="s">
+      <c r="D155" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="B149" s="4" t="s">
+      <c r="B156" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="C149" s="4" t="s">
+      <c r="C156" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="D149" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" ht="25" x14ac:dyDescent="0.25">
-      <c r="A150" s="4" t="s">
+      <c r="D156" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="B157" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="C150" s="4" t="s">
+      <c r="C157" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="D150" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" ht="25" x14ac:dyDescent="0.25">
-      <c r="A151" s="4" t="s">
+      <c r="D157" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B158" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="C151" s="4" t="s">
+      <c r="C158" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="D151" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" ht="25" x14ac:dyDescent="0.25">
-      <c r="A152" s="4" t="s">
+      <c r="D158" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="B159" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="C152" s="4" t="s">
+      <c r="C159" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="D152" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" ht="25" x14ac:dyDescent="0.25">
-      <c r="A153" s="4" t="s">
+      <c r="D159" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="25" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="B153" s="4" t="s">
+      <c r="B160" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="C153" s="4" t="s">
+      <c r="C160" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="D153" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" ht="25" x14ac:dyDescent="0.25">
-      <c r="A154" s="4" t="s">
+      <c r="D160" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="B154" s="4" t="s">
+      <c r="B161" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="C154" s="4" t="s">
+      <c r="C161" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="D154" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" ht="25" x14ac:dyDescent="0.25">
-      <c r="A155" s="4" t="s">
+      <c r="D161" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B162" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C155" s="4" t="s">
+      <c r="C162" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="D155" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" ht="25" x14ac:dyDescent="0.25">
-      <c r="A156" s="4" t="s">
+      <c r="D162" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="B156" s="4" t="s">
+      <c r="B163" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="C156" s="4" t="s">
+      <c r="C163" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="D156" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" ht="100" x14ac:dyDescent="0.25">
-      <c r="A157" s="4" t="s">
+      <c r="D163" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="100" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="B157" s="4" t="s">
+      <c r="B164" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="C157" s="4" t="s">
+      <c r="C164" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="D157" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" ht="25" x14ac:dyDescent="0.25">
-      <c r="A158" s="4" t="s">
+      <c r="D164" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="B158" s="4" t="s">
+      <c r="B165" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="C158" s="4" t="s">
+      <c r="C165" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="D158" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" ht="25" x14ac:dyDescent="0.25">
-      <c r="A159" s="4" t="s">
+      <c r="D165" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="B159" s="4" t="s">
+      <c r="B166" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="C159" s="4" t="s">
+      <c r="C166" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="D159" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" ht="25" x14ac:dyDescent="0.25">
-      <c r="A160" s="4" t="s">
+      <c r="D166" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B167" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="C160" s="4" t="s">
+      <c r="C167" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="D160" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A161" s="6" t="s">
+      <c r="D167" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A168" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="B161" s="6" t="s">
+      <c r="B168" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="C161" s="6" t="s">
+      <c r="C168" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D161" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="E161" s="7" t="s">
+      <c r="D168" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="E168" s="7" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A162" s="4" t="s">
+    <row r="169" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="B162" s="4" t="s">
+      <c r="B169" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="C162" s="4" t="s">
+      <c r="C169" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="D162" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" ht="25" x14ac:dyDescent="0.25">
-      <c r="A163" s="4" t="s">
+      <c r="D169" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="B163" s="4" t="s">
+      <c r="B170" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="C163" s="4" t="s">
+      <c r="C170" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="D163" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A164" s="4" t="s">
+      <c r="D170" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="B164" s="4" t="s">
+      <c r="B171" s="4" t="s">
         <v>487</v>
       </c>
-      <c r="C164" s="4" t="s">
+      <c r="C171" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="D164" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" s="4" t="s">
+      <c r="D171" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="B165" s="4" t="s">
+      <c r="B172" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="C165" s="4" t="s">
+      <c r="C172" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="D165" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" ht="25" x14ac:dyDescent="0.25">
-      <c r="A166" s="4" t="s">
+      <c r="D172" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="B166" s="4" t="s">
+      <c r="B173" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="C166" s="4" t="s">
+      <c r="C173" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="D166" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" ht="25" x14ac:dyDescent="0.25">
-      <c r="A167" s="4" t="s">
+      <c r="D173" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="B167" s="4" t="s">
+      <c r="B174" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="C167" s="4" t="s">
+      <c r="C174" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="D167" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" ht="25" x14ac:dyDescent="0.25">
-      <c r="A168" s="4" t="s">
+      <c r="D174" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A175" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="B168" s="4" t="s">
+      <c r="B175" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="C168" s="4" t="s">
+      <c r="C175" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="D168" s="3" t="s">
-        <v>503</v>
-      </c>
+      <c r="D175" s="9" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A176" s="10">
+        <v>441</v>
+      </c>
+      <c r="B176" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="C176" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="D176" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="E176" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="F176" s="12"/>
+    </row>
+    <row r="177" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A177" s="10">
+        <v>461</v>
+      </c>
+      <c r="B177" s="10" t="s">
+        <v>506</v>
+      </c>
+      <c r="C177" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="D177" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="E177" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="F177" s="12"/>
+    </row>
+    <row r="178" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A178" s="10">
+        <v>489</v>
+      </c>
+      <c r="B178" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="C178" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="D178" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="E178" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="F178" s="12"/>
+    </row>
+    <row r="179" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A179" s="10">
+        <v>490</v>
+      </c>
+      <c r="B179" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="C179" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="D179" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="E179" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="F179" s="12"/>
+    </row>
+    <row r="180" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A180" s="10">
+        <v>493</v>
+      </c>
+      <c r="B180" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="C180" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="D180" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="E180" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="F180" s="12"/>
+    </row>
+    <row r="181" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A181" s="10">
+        <v>494</v>
+      </c>
+      <c r="B181" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="C181" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="D181" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="E181" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="F181" s="12"/>
+    </row>
+    <row r="182" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A182" s="10">
+        <v>495</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="C182" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="D182" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="E182" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="F182" s="12"/>
+    </row>
+    <row r="183" spans="1:6" ht="25" x14ac:dyDescent="0.25">
+      <c r="A183" s="10">
+        <v>498</v>
+      </c>
+      <c r="B183" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="C183" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="D183" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="E183" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="F183" s="12"/>
+    </row>
+    <row r="184" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A184" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
